--- a/Data/ConfigRuntime.xlsx
+++ b/Data/ConfigRuntime.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\clescm0002\rpa\01. Procesos\FRAMEWORKS\Clarke\ClarkeREFramework_Reporter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E_MMH242\Documents\UiPath\Template\ExtendedREFramework_Reporter\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="157">
   <si>
     <t>Name</t>
   </si>
@@ -166,9 +166,6 @@
     <t>DBConnectionString</t>
   </si>
   <si>
-    <t>CredMail</t>
-  </si>
-  <si>
     <t>Relative path (folder name) of shared folder for "input" files (downloaded files)</t>
   </si>
   <si>
@@ -187,12 +184,6 @@
     <t>Name of the "main" Database table</t>
   </si>
   <si>
-    <t>SMTPHost</t>
-  </si>
-  <si>
-    <t>SMTPPort</t>
-  </si>
-  <si>
     <t>ItemDataTable</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>RPA CoE</t>
   </si>
   <si>
-    <t>ClarkeRPA_SMTPHost</t>
-  </si>
-  <si>
     <t>JCV001_XXX</t>
   </si>
   <si>
@@ -244,9 +232,6 @@
     <t>Name of the folders that will be created in shared folder. Use process (long) name</t>
   </si>
   <si>
-    <t xml:space="preserve">"BasePathName" + "EndpointPathName" will be joined. </t>
-  </si>
-  <si>
     <t>InputPath</t>
   </si>
   <si>
@@ -295,54 +280,21 @@
     <t>JCV_Test</t>
   </si>
   <si>
-    <t>ClarkeRPA_SMTPPort</t>
-  </si>
-  <si>
     <t>MAIL_ROBOT</t>
   </si>
   <si>
-    <t>ClarkeRPA_DBConnectionString</t>
-  </si>
-  <si>
-    <t>ClarkeRPA_SharedFolder_Base</t>
-  </si>
-  <si>
     <t>Process name that will be sent in emails</t>
   </si>
   <si>
     <t>MailProcessFullName</t>
   </si>
   <si>
-    <t>MailProcessShortName</t>
-  </si>
-  <si>
-    <t>MailProcessNickName</t>
-  </si>
-  <si>
-    <t>Dora</t>
-  </si>
-  <si>
-    <t>PRN</t>
-  </si>
-  <si>
     <t>MailSenderName</t>
   </si>
   <si>
-    <t>NoReply ClarkeModet</t>
-  </si>
-  <si>
     <t>Name that will be sent on emails</t>
   </si>
   <si>
-    <t>ConstantesTemplatesMail</t>
-  </si>
-  <si>
-    <t>MailCountry</t>
-  </si>
-  <si>
-    <t>España</t>
-  </si>
-  <si>
     <t>ConstantesEnvioMail</t>
   </si>
   <si>
@@ -352,190 +304,150 @@
     <t>Usuario</t>
   </si>
   <si>
-    <t>Plantilla_EmailComunicacion</t>
-  </si>
-  <si>
-    <t>Plantilla_EmailTerminated</t>
-  </si>
-  <si>
-    <t>Plantilla_EmailComienzo</t>
-  </si>
-  <si>
-    <t>Plantilla_EmailErrorNegocio</t>
-  </si>
-  <si>
-    <t>Subject_EmailErrorNegocio</t>
-  </si>
-  <si>
-    <t>Subject_EmailComienzo</t>
-  </si>
-  <si>
-    <t>Subject_EmailComunicacion</t>
-  </si>
-  <si>
-    <t>Subject_EmailTerminated</t>
-  </si>
-  <si>
-    <t>Sust_NombreProceso</t>
-  </si>
-  <si>
-    <t>SustitucionesTemplatesMail</t>
-  </si>
-  <si>
-    <t>Sust_NombreCortoProceso</t>
-  </si>
-  <si>
-    <t>Sust_Usuario</t>
-  </si>
-  <si>
-    <t>Sust_ApodoProceso</t>
-  </si>
-  <si>
-    <t>Sust_Pais</t>
-  </si>
-  <si>
-    <t>Plantilla_EmailFinished</t>
-  </si>
-  <si>
-    <t>Sust_FechaTransaccion</t>
-  </si>
-  <si>
-    <t>Sust_CodigoExcepcion</t>
-  </si>
-  <si>
-    <t>Sust_IDTransaccion</t>
-  </si>
-  <si>
-    <t>Sust_IDTransaccion2</t>
-  </si>
-  <si>
-    <t>Sust_DescripciónTransaccion</t>
-  </si>
-  <si>
-    <t>Sust_DescripcionExcepcion</t>
-  </si>
-  <si>
-    <t>Sust_FechaComienzoEjecución</t>
-  </si>
-  <si>
-    <t>Sust_TextoCuerpo</t>
-  </si>
-  <si>
-    <t>Sust_FechaEjec</t>
-  </si>
-  <si>
-    <t>Sust_IDEjec</t>
-  </si>
-  <si>
-    <t>Subject_EmailFinished</t>
-  </si>
-  <si>
-    <t>Sust_Modulo</t>
-  </si>
-  <si>
-    <t>[Nombre Proceso]</t>
-  </si>
-  <si>
-    <t>[Fecha Comienzo Ejecución]</t>
-  </si>
-  <si>
-    <t>[Usuario]</t>
-  </si>
-  <si>
-    <t>[Nombre Corto Proceso]</t>
-  </si>
-  <si>
-    <t>[Apodo Proceso]</t>
-  </si>
-  <si>
-    <t>[Pais]</t>
-  </si>
-  <si>
-    <t>[TEXTO]</t>
-  </si>
-  <si>
-    <t>[ID Transacción]</t>
-  </si>
-  <si>
-    <t>[Id Transacción]</t>
-  </si>
-  <si>
-    <t>[Código Excepción]</t>
-  </si>
-  <si>
-    <t>[Descripción Excepción]</t>
-  </si>
-  <si>
-    <t>[Fecha Creación Transacción]</t>
-  </si>
-  <si>
-    <t>[Descripción]</t>
-  </si>
-  <si>
-    <t>[Fecha Fin Ejecución]</t>
-  </si>
-  <si>
-    <t>[ID Ejecución]</t>
-  </si>
-  <si>
-    <t>[Modulo]</t>
-  </si>
-  <si>
-    <t>\\CLESCM0002\rpa\05. Templates\02. Produccion\01. Emails\PlantillaProceso_Comienzo.htm</t>
-  </si>
-  <si>
-    <t>\\CLESCM0002\rpa\05. Templates\02. Produccion\01. Emails\PlantillaProceso_ComunicaciónGeneral.htm</t>
-  </si>
-  <si>
-    <t>\\CLESCM0002\rpa\05. Templates\02. Produccion\01. Emails\PlantillaProceso_Terminated.htm</t>
-  </si>
-  <si>
-    <t>\\CLESCM0002\rpa\05. Templates\02. Produccion\01. Emails\PlantillaProceso_ExcepcionNegocio.htm</t>
-  </si>
-  <si>
-    <t>\\CLESCM0002\rpa\05. Templates\02. Produccion\01. Emails\PlantillaProceso_Finalizado.htm</t>
-  </si>
-  <si>
     <t>PRN001_PRN_PRN</t>
   </si>
   <si>
-    <t>[RPA] - [Nombre Proceso] - Comunicación</t>
-  </si>
-  <si>
-    <t>[RPA] - [Nombre Proceso] - Ejecución Fallida</t>
-  </si>
-  <si>
-    <t>[RPA] - [Nombre Proceso] - Comienzo</t>
-  </si>
-  <si>
-    <t>[RPA] - [Nombre Proceso] - Excepción de Negocio</t>
-  </si>
-  <si>
-    <t>[RPA] - [Nombre Proceso] - Ejecución Finalizada</t>
-  </si>
-  <si>
-    <t>Sust_FechaFaultedEjec</t>
-  </si>
-  <si>
-    <t>[Fecha Ejecución]</t>
-  </si>
-  <si>
-    <t>MailCCO_All</t>
-  </si>
-  <si>
     <t>jmcaravaca@minsait.com</t>
   </si>
   <si>
     <t>ProcessModule</t>
   </si>
   <si>
-    <t>Colector/Consumidor</t>
+    <t>MailContactLanguage</t>
+  </si>
+  <si>
+    <t>es-ES</t>
+  </si>
+  <si>
+    <t>MailTO_All</t>
+  </si>
+  <si>
+    <t>MailCC_All</t>
+  </si>
+  <si>
+    <t>MailBCC_All</t>
+  </si>
+  <si>
+    <t>MailTO_Exceptions</t>
+  </si>
+  <si>
+    <t>MailCC_Exceptions</t>
+  </si>
+  <si>
+    <t>MailBCC_Exceptions</t>
+  </si>
+  <si>
+    <t>CAMBIAR</t>
+  </si>
+  <si>
+    <t>SendMail</t>
+  </si>
+  <si>
+    <t>QueueNameNextStep</t>
+  </si>
+  <si>
+    <t>ItemTableNextStep</t>
+  </si>
+  <si>
+    <t>Name of the "main" Database table for the next step</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Orchestrator queue Name for the Next step. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Leave empty i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>f this is the final step last "consumidor"). The value must match with the queue name defined on Orchestrator.</t>
+    </r>
+  </si>
+  <si>
+    <t>NO CAMBIAR</t>
+  </si>
+  <si>
+    <t>ConstantesCarpetas</t>
+  </si>
+  <si>
+    <t>RPA_DBConnectionString</t>
+  </si>
+  <si>
+    <t>RPA_SharedFolder_Base</t>
+  </si>
+  <si>
+    <t>NoReply</t>
+  </si>
+  <si>
+    <t>UseDB</t>
+  </si>
+  <si>
+    <t>Use auxiliary database for error codes and item data</t>
+  </si>
+  <si>
+    <t>UseDataServiceErrors</t>
+  </si>
+  <si>
+    <t>UseDataServiceItem</t>
+  </si>
+  <si>
+    <t>Use Data service for item data</t>
+  </si>
+  <si>
+    <t>Use Data service for error codes</t>
+  </si>
+  <si>
+    <t>ExceptionLanguage</t>
+  </si>
+  <si>
+    <t>EnforceSecondDataSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If set to true, framework will attempt to get data from relevant data source (DB/Data Service). If data doesn't exist, an exception will be htrown . If false, it will not try to retrieve data from data source </t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Windows(\)</t>
+  </si>
+  <si>
+    <t>Unix(/)</t>
+  </si>
+  <si>
+    <t>Add failed items to next queue already as failed</t>
+  </si>
+  <si>
+    <t>AddFailedItem</t>
   </si>
   <si>
     <t>LastReportingTime</t>
   </si>
   <si>
-    <t>Last Reporting time in "o" format</t>
+    <t>JCV_LastReportingTime</t>
+  </si>
+  <si>
+    <t>Name of the last reporting time asset</t>
+  </si>
+  <si>
+    <t>LastReportTimeAssetName</t>
+  </si>
+  <si>
+    <t>ErrorCodePath</t>
+  </si>
+  <si>
+    <t>Data\ErrorCodes.xlsx</t>
   </si>
   <si>
     <t>TemplateReport</t>
@@ -544,43 +456,67 @@
     <t>Data\Template_Report.xlsx</t>
   </si>
   <si>
+    <t>ReportName</t>
+  </si>
+  <si>
     <t>SheetDetails</t>
   </si>
   <si>
+    <t>Detalle</t>
+  </si>
+  <si>
     <t>SheetSummary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>JCV_LastReportingDate</t>
-  </si>
-  <si>
-    <t>Detalle</t>
-  </si>
-  <si>
-    <t>MailTO</t>
-  </si>
-  <si>
-    <t>MailCC</t>
-  </si>
-  <si>
-    <t>MailBCC</t>
+    <t>Reporter</t>
+  </si>
+  <si>
+    <t>Reportname_{0}.xlsx</t>
+  </si>
+  <si>
+    <t>NoReplyMail</t>
   </si>
   <si>
     <t>MailBody</t>
   </si>
   <si>
-    <t>Adjunto se encuentra el reporte operativo del proceso.</t>
-  </si>
-  <si>
-    <t>Always keep a {0} in the file name to add the date</t>
-  </si>
-  <si>
-    <t>ReportName</t>
-  </si>
-  <si>
-    <t>Reporte{0}.xlsx</t>
+    <t>Modify as required</t>
+  </si>
+  <si>
+    <t>Adjuntamos reporte de ejecución</t>
+  </si>
+  <si>
+    <t>AnalyticsJobsList</t>
+  </si>
+  <si>
+    <t>UseAnalytics</t>
+  </si>
+  <si>
+    <t>Job names involved in the process separated by ",". (NOT process names, if they are different)</t>
+  </si>
+  <si>
+    <t>Whether to enable the Analytics functionality</t>
+  </si>
+  <si>
+    <t>JobVerification</t>
+  </si>
+  <si>
+    <t>Set to FALSO only if not all jobs listed above will run periodically (for example, if your process runs daily but has a one-off monthly job that won't always be present when running the Reporter)</t>
+  </si>
+  <si>
+    <t>Attended Job</t>
+  </si>
+  <si>
+    <t>AnalyticsTable</t>
+  </si>
+  <si>
+    <t>Analytics database table</t>
+  </si>
+  <si>
+    <t>dbo.AnalyticsData</t>
   </si>
 </sst>
 </file>
@@ -619,9 +555,8 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -649,11 +584,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -666,11 +600,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -983,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z997"/>
+  <dimension ref="A1:Z1018"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1031,160 +963,306 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="45">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="30">
-      <c r="A5" t="s">
+    <row r="6" spans="1:26">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="30">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B13" t="s">
-        <v>176</v>
-      </c>
+    <row r="13" spans="1:26">
+      <c r="B13" s="2"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
+        <v>114</v>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="18" spans="1:2" ht="14.25" customHeight="1">
+        <v>106</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.25" customHeight="1">
+        <v>117</v>
+      </c>
+      <c r="B18" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.25" customHeight="1">
+        <v>121</v>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="22" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="24" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="26" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+        <v>120</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="35" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2134,6 +2212,27 @@
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
+    <row r="1002" ht="14.25" customHeight="1"/>
+    <row r="1003" ht="14.25" customHeight="1"/>
+    <row r="1004" ht="14.25" customHeight="1"/>
+    <row r="1005" ht="14.25" customHeight="1"/>
+    <row r="1006" ht="14.25" customHeight="1"/>
+    <row r="1007" ht="14.25" customHeight="1"/>
+    <row r="1008" ht="14.25" customHeight="1"/>
+    <row r="1009" ht="14.25" customHeight="1"/>
+    <row r="1010" ht="14.25" customHeight="1"/>
+    <row r="1011" ht="14.25" customHeight="1"/>
+    <row r="1012" ht="14.25" customHeight="1"/>
+    <row r="1013" ht="14.25" customHeight="1"/>
+    <row r="1014" ht="14.25" customHeight="1"/>
+    <row r="1015" ht="14.25" customHeight="1"/>
+    <row r="1016" ht="14.25" customHeight="1"/>
+    <row r="1017" ht="14.25" customHeight="1"/>
+    <row r="1018" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2143,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z982"/>
+  <dimension ref="A1:Z949"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -2202,7 +2301,7 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
@@ -2323,116 +2422,123 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
@@ -2447,305 +2553,124 @@
     </row>
     <row r="35" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>89</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
-        <v>99</v>
-      </c>
-      <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-    </row>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" t="s">
-        <v>104</v>
+        <v>148</v>
+      </c>
+      <c r="B40" t="b">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A42" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B44" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="b">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="50" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A50" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A54" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A55" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A56" t="s">
-        <v>116</v>
-      </c>
-      <c r="B56" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A57" t="s">
-        <v>118</v>
-      </c>
-      <c r="B57" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A58" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A59" t="s">
-        <v>120</v>
-      </c>
-      <c r="B59" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A60" t="s">
-        <v>121</v>
-      </c>
-      <c r="B60" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A61" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A62" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A63" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A65" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A66" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A67" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A68" t="s">
-        <v>131</v>
-      </c>
-      <c r="B68" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A69" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A70" t="s">
-        <v>134</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A71" t="s">
-        <v>128</v>
-      </c>
-      <c r="B71" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A72" t="s">
-        <v>162</v>
-      </c>
-      <c r="B72" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="74" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="75" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="76" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="77" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="78" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="79" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="80" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
     <row r="81" ht="14.25" customHeight="1"/>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -3615,56 +3540,16 @@
     <row r="947" ht="14.25" customHeight="1"/>
     <row r="948" ht="14.25" customHeight="1"/>
     <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B44" r:id="rId1"/>
-    <hyperlink ref="B45" r:id="rId2"/>
-    <hyperlink ref="B46" r:id="rId3"/>
-    <hyperlink ref="B47" r:id="rId4"/>
-    <hyperlink ref="B48" r:id="rId5"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z999"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -3711,51 +3596,31 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" t="s">
-        <v>169</v>
-      </c>
-    </row>
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4748,8 +4613,6 @@
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4808,21 +4671,21 @@
         <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -5829,15 +5692,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z999"/>
+  <dimension ref="A1:AA998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="27" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1">
+    <row r="1" spans="1:27" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5848,9 +5712,11 @@
         <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -5872,28 +5738,34 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-    </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="D2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
+      <c r="AA1" s="1"/>
+    </row>
+    <row r="2" spans="1:27" ht="14.25" customHeight="1">
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="14.25" customHeight="1">
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:27" ht="14.25" customHeight="1">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:27" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:27" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -6876,8 +6748,12 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576">
+      <formula1>"Windows(\),Unix(/)"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Data/ConfigRuntime.xlsx
+++ b/Data/ConfigRuntime.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="160">
   <si>
     <t>Name</t>
   </si>
@@ -504,12 +504,6 @@
     <t>JobVerification</t>
   </si>
   <si>
-    <t>Set to FALSO only if not all jobs listed above will run periodically (for example, if your process runs daily but has a one-off monthly job that won't always be present when running the Reporter)</t>
-  </si>
-  <si>
-    <t>Attended Job</t>
-  </si>
-  <si>
     <t>AnalyticsTable</t>
   </si>
   <si>
@@ -517,6 +511,21 @@
   </si>
   <si>
     <t>dbo.AnalyticsData</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>DBProcessId</t>
+  </si>
+  <si>
+    <t>Process id inside the database table that matches processes to their ids</t>
+  </si>
+  <si>
+    <t>PlaceholderJob,AnotherPlaceholderJob</t>
+  </si>
+  <si>
+    <t>Set to false only if not all jobs listed above will run periodically (for example, if your process runs daily but has a one-off monthly job that won't always be present when running the Reporter)</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -601,6 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1018"/>
+  <dimension ref="A1:Z1023"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1131,138 +1141,188 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="C22" s="4"/>
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" s="2" t="s">
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" t="s">
-        <v>102</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>93</v>
       </c>
+      <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
         <v>144</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B36" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C36" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="B32" s="8"/>
-    </row>
-    <row r="33" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A33" t="s">
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="B37" s="8"/>
+    </row>
+    <row r="38" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A38" t="s">
         <v>94</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B38" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="35" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A35" t="s">
+    <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A40" t="s">
         <v>95</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B40" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
+    <row r="41" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A41" t="s">
         <v>104</v>
       </c>
-      <c r="B36" t="b">
+      <c r="B41" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="38" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
+    <row r="42" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
         <v>131</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B43" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A44" t="s">
         <v>132</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B44" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="41" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="42" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="43" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="44" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="46" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="47" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="48" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2233,6 +2293,11 @@
     <row r="1016" ht="14.25" customHeight="1"/>
     <row r="1017" ht="14.25" customHeight="1"/>
     <row r="1018" ht="14.25" customHeight="1"/>
+    <row r="1019" ht="14.25" customHeight="1"/>
+    <row r="1020" ht="14.25" customHeight="1"/>
+    <row r="1021" ht="14.25" customHeight="1"/>
+    <row r="1022" ht="14.25" customHeight="1"/>
+    <row r="1023" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2590,50 +2655,6 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>148</v>
-      </c>
-      <c r="B40" t="b">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A41" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" t="s">
-        <v>156</v>
-      </c>
-      <c r="C41" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A42" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" t="b">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>152</v>
-      </c>
-    </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="46" spans="1:3" ht="14.25" customHeight="1"/>

--- a/Data/ConfigRuntime.xlsx
+++ b/Data/ConfigRuntime.xlsx
@@ -522,10 +522,10 @@
     <t>Process id inside the database table that matches processes to their ids</t>
   </si>
   <si>
-    <t>PlaceholderJob,AnotherPlaceholderJob</t>
-  </si>
-  <si>
     <t>Set to false only if not all jobs listed above will run periodically (for example, if your process runs daily but has a one-off monthly job that won't always be present when running the Reporter)</t>
+  </si>
+  <si>
+    <t>DispatcherJob,PerformerJob</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1178,7 @@
         <v>147</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
         <v>149</v>
@@ -1192,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">

--- a/Data/ConfigRuntime.xlsx
+++ b/Data/ConfigRuntime.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E_MMH242\Documents\UiPath\Template\ExtendedREFramework_Reporter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E_MMH242\Documents\UiPath\Templates\ExtendedREFramework_Reporter\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,14 +16,64 @@
     <sheet name="Constants" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" r:id="rId3"/>
     <sheet name="Credentials" sheetId="5" r:id="rId4"/>
-    <sheet name="Paths" sheetId="7" r:id="rId5"/>
+    <sheet name="Drives" sheetId="8" r:id="rId5"/>
+    <sheet name="Paths" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MORELL HIGUERAS, MARC</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>You can use this as the BasePathName in sheet Paths</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Name within sheet Assets containing the value of the path to map onto the drive</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Drives should only be mapped when a credential is required to access a network resource. Otherwise, use the server path.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="167">
   <si>
     <t>Name</t>
   </si>
@@ -527,12 +577,33 @@
   <si>
     <t>DispatcherJob,PerformerJob</t>
   </si>
+  <si>
+    <t>CheckReadyToReport</t>
+  </si>
+  <si>
+    <t>If enabled, runs the "CheckIsReadyToReport" workflow. By default ensures the queue has no pending items before reporting.</t>
+  </si>
+  <si>
+    <t>MinutesSuspended</t>
+  </si>
+  <si>
+    <t>When CheckReadyToReport is true, amount of minutes the job will be suspended between readiness checks. Must be an integer value.</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>Asset Path</t>
+  </si>
+  <si>
+    <t>Credential</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -569,6 +640,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -596,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -611,6 +695,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -925,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1023"/>
+  <dimension ref="A1:Z1024"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1008,232 +1101,235 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="4"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="30">
-      <c r="A12" t="s">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="30">
+      <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>115</v>
-      </c>
+    <row r="14" spans="1:26">
+      <c r="B14" s="2"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
+        <v>114</v>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" t="b">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" t="b">
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B19" t="b">
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A21" t="s">
         <v>120</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" t="b">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>150</v>
-      </c>
+      <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>152</v>
-      </c>
-      <c r="B23" t="s">
-        <v>154</v>
+        <v>148</v>
+      </c>
+      <c r="B23" t="b">
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" t="s">
-        <v>149</v>
+        <v>156</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
         <v>151</v>
       </c>
-      <c r="B26" t="b">
+      <c r="B27" t="b">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1">
-      <c r="C27" s="4"/>
-    </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>93</v>
       </c>
+      <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A32" t="s">
-        <v>99</v>
+      <c r="A32" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>93</v>
@@ -1241,23 +1337,23 @@
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>101</v>
+      <c r="A34" t="s">
+        <v>100</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A35" t="s">
-        <v>102</v>
+      <c r="A35" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>93</v>
@@ -1265,61 +1361,68 @@
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A37" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B37" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1">
-      <c r="B37" s="8"/>
-    </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
+      <c r="B38" s="8"/>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
         <v>94</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-    </row>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
         <v>104</v>
       </c>
-      <c r="B41" t="b">
+      <c r="B42" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" t="s">
-        <v>129</v>
-      </c>
-    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2298,6 +2401,7 @@
     <row r="1021" ht="14.25" customHeight="1"/>
     <row r="1022" ht="14.25" customHeight="1"/>
     <row r="1023" ht="14.25" customHeight="1"/>
+    <row r="1024" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2307,7 +2411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z949"/>
+  <dimension ref="A1:Z950"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -2372,290 +2476,300 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:26" ht="30">
+      <c r="A4" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="12">
+        <v>5</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="45">
-      <c r="A17" t="s">
+    <row r="17" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:3" ht="45">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="b">
+      <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="19" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A20" t="s">
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A21" t="s">
         <v>53</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-    </row>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="2" t="b">
+      <c r="B28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A36" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
         <v>90</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3561,6 +3675,7 @@
     <row r="947" ht="14.25" customHeight="1"/>
     <row r="948" ht="14.25" customHeight="1"/>
     <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5712,6 +5827,44 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="3" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="A single uppercase letter, A-Z" sqref="B2:B27">
+      <formula1>"A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V,W,X,Y,Z"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
